--- a/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202608/AllSymbols_P&L_20260806.xlsx
+++ b/1. Reporting_Data/IB_Mark-to-Market PnL/AllSymbols/2026/202608/AllSymbols_P&L_20260806.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="339" uniqueCount="109">
   <si>
     <t>Symbol</t>
   </si>
@@ -43,6 +43,39 @@
     <t>Market Value USD</t>
   </si>
   <si>
+    <t>001040.KS</t>
+  </si>
+  <si>
+    <t>003690.KS</t>
+  </si>
+  <si>
+    <t>004170.KS</t>
+  </si>
+  <si>
+    <t>006800.KS</t>
+  </si>
+  <si>
+    <t>011070.KS</t>
+  </si>
+  <si>
+    <t>023530.KS</t>
+  </si>
+  <si>
+    <t>028670.KS</t>
+  </si>
+  <si>
+    <t>039490.KS</t>
+  </si>
+  <si>
+    <t>069960.KS</t>
+  </si>
+  <si>
+    <t>2914.T</t>
+  </si>
+  <si>
+    <t>377300.KS</t>
+  </si>
+  <si>
     <t>6301.T</t>
   </si>
   <si>
@@ -106,6 +139,9 @@
     <t>CTAS</t>
   </si>
   <si>
+    <t>CVX</t>
+  </si>
+  <si>
     <t>D05</t>
   </si>
   <si>
@@ -127,6 +163,9 @@
     <t>ETN</t>
   </si>
   <si>
+    <t>EWH</t>
+  </si>
+  <si>
     <t>EWY</t>
   </si>
   <si>
@@ -181,6 +220,9 @@
     <t>O</t>
   </si>
   <si>
+    <t>O39</t>
+  </si>
+  <si>
     <t>PANW</t>
   </si>
   <si>
@@ -205,6 +247,9 @@
     <t>SCJ</t>
   </si>
   <si>
+    <t>SHELl</t>
+  </si>
+  <si>
     <t>SHLD</t>
   </si>
   <si>
@@ -268,9 +313,15 @@
     <t>UTES</t>
   </si>
   <si>
+    <t>KRW</t>
+  </si>
+  <si>
     <t>HKD</t>
   </si>
   <si>
+    <t>TWD</t>
+  </si>
+  <si>
     <t>JPY</t>
   </si>
   <si>
@@ -278,6 +329,9 @@
   </si>
   <si>
     <t>USD</t>
+  </si>
+  <si>
+    <t>GBP</t>
   </si>
   <si>
     <t>Equity</t>
@@ -644,7 +698,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I92"/>
+  <dimension ref="A1:I121"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -677,2641 +731,3482 @@
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2">
-        <v>1109</v>
+      <c r="A2" t="s">
+        <v>9</v>
       </c>
       <c r="B2">
-        <v>2000</v>
+        <v>411</v>
       </c>
       <c r="C2">
-        <v>32.86</v>
+        <v>145900</v>
       </c>
       <c r="D2">
-        <v>-56.09</v>
+        <v>2339.13</v>
       </c>
       <c r="E2">
-        <v>65720</v>
+        <v>59964900</v>
       </c>
       <c r="F2" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G2" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H2">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I2">
-        <v>8379.299999999999</v>
+        <v>41975.43</v>
       </c>
     </row>
     <row r="3" spans="1:9">
-      <c r="A3">
-        <v>1258</v>
+      <c r="A3" t="s">
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>1000</v>
+        <v>12535</v>
       </c>
       <c r="C3">
-        <v>15.96</v>
+        <v>14630</v>
       </c>
       <c r="D3">
-        <v>-3.82</v>
+        <v>7045.97</v>
       </c>
       <c r="E3">
-        <v>15960</v>
+        <v>183387050</v>
       </c>
       <c r="F3" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G3" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H3">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I3">
-        <v>2034.9</v>
+        <v>128370.94</v>
       </c>
     </row>
     <row r="4" spans="1:9">
-      <c r="A4">
-        <v>1288</v>
+      <c r="A4" t="s">
+        <v>11</v>
       </c>
       <c r="B4">
-        <v>6000</v>
+        <v>95</v>
       </c>
       <c r="C4">
-        <v>5.935</v>
+        <v>427500</v>
       </c>
       <c r="D4">
-        <v>-3.82</v>
+        <v>-166.87</v>
       </c>
       <c r="E4">
-        <v>35610</v>
+        <v>40612500</v>
       </c>
       <c r="F4" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G4" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H4">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I4">
-        <v>4540.27</v>
+        <v>28428.75</v>
       </c>
     </row>
     <row r="5" spans="1:9">
-      <c r="A5">
-        <v>1398</v>
+      <c r="A5" t="s">
+        <v>12</v>
       </c>
       <c r="B5">
-        <v>1566000</v>
+        <v>3751</v>
       </c>
       <c r="C5">
-        <v>7.2</v>
+        <v>34550</v>
       </c>
       <c r="D5">
-        <v>-998.09</v>
+        <v>-1713.12</v>
       </c>
       <c r="E5">
-        <v>11275200</v>
+        <v>129597050</v>
       </c>
       <c r="F5" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G5" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H5">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I5">
-        <v>1437588</v>
+        <v>90717.94</v>
       </c>
     </row>
     <row r="6" spans="1:9">
-      <c r="A6">
-        <v>1698</v>
+      <c r="A6" t="s">
+        <v>13</v>
       </c>
       <c r="B6">
-        <v>2000</v>
+        <v>8</v>
       </c>
       <c r="C6">
-        <v>37.4</v>
+        <v>554000</v>
       </c>
       <c r="D6">
-        <v>-50.99</v>
+        <v>-264.19</v>
       </c>
       <c r="E6">
-        <v>74800</v>
+        <v>4432000</v>
       </c>
       <c r="F6" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G6" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H6">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I6">
-        <v>9537</v>
+        <v>3102.4</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7">
-        <v>1810</v>
+        <v>11200</v>
       </c>
       <c r="B7">
-        <v>200</v>
+        <v>4067</v>
       </c>
       <c r="C7">
-        <v>26.86</v>
+        <v>21400</v>
       </c>
       <c r="D7">
-        <v>-19.89</v>
+        <v>857.28</v>
       </c>
       <c r="E7">
-        <v>5372</v>
+        <v>87033800</v>
       </c>
       <c r="F7" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G7" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H7">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I7">
-        <v>684.9299999999999</v>
+        <v>60923.66</v>
       </c>
     </row>
     <row r="8" spans="1:9">
-      <c r="A8">
-        <v>2359</v>
+      <c r="A8" t="s">
+        <v>14</v>
       </c>
       <c r="B8">
-        <v>300</v>
+        <v>485</v>
       </c>
       <c r="C8">
-        <v>179.7</v>
+        <v>114500</v>
       </c>
       <c r="D8">
-        <v>-145.32</v>
+        <v>68.16</v>
       </c>
       <c r="E8">
-        <v>53910</v>
+        <v>55532500</v>
       </c>
       <c r="F8" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G8" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H8">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I8">
-        <v>6873.52</v>
+        <v>38872.75</v>
       </c>
     </row>
     <row r="9" spans="1:9">
-      <c r="A9">
-        <v>2800</v>
+      <c r="A9" t="s">
+        <v>15</v>
       </c>
       <c r="B9">
-        <v>2000</v>
+        <v>15933</v>
       </c>
       <c r="C9">
-        <v>26</v>
+        <v>5850</v>
       </c>
       <c r="D9">
-        <v>-101.98</v>
+        <v>-111.95</v>
       </c>
       <c r="E9">
-        <v>52000</v>
+        <v>93208050</v>
       </c>
       <c r="F9" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G9" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H9">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I9">
-        <v>6630</v>
+        <v>65245.64</v>
       </c>
     </row>
     <row r="10" spans="1:9">
-      <c r="A10">
-        <v>2828</v>
+      <c r="A10" t="s">
+        <v>16</v>
       </c>
       <c r="B10">
-        <v>600</v>
+        <v>268</v>
       </c>
       <c r="C10">
-        <v>87.54000000000001</v>
+        <v>290500</v>
       </c>
       <c r="D10">
-        <v>-76.48</v>
+        <v>-376.61</v>
       </c>
       <c r="E10">
-        <v>52524</v>
+        <v>77854000</v>
       </c>
       <c r="F10" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G10" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H10">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I10">
-        <v>6696.81</v>
+        <v>54497.8</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11">
-        <v>2899</v>
+        <v>51900</v>
       </c>
       <c r="B11">
-        <v>2000</v>
+        <v>765</v>
       </c>
       <c r="C11">
-        <v>35.3</v>
+        <v>324000</v>
       </c>
       <c r="D11">
-        <v>25.49</v>
+        <v>16931.63</v>
       </c>
       <c r="E11">
-        <v>70600</v>
+        <v>247860000</v>
       </c>
       <c r="F11" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G11" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H11">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I11">
-        <v>9001.5</v>
+        <v>173502</v>
       </c>
     </row>
     <row r="12" spans="1:9">
-      <c r="A12">
-        <v>3067</v>
+      <c r="A12" t="s">
+        <v>17</v>
       </c>
       <c r="B12">
-        <v>700</v>
+        <v>1441</v>
       </c>
       <c r="C12">
-        <v>10.18</v>
+        <v>106400</v>
       </c>
       <c r="D12">
-        <v>-19.63</v>
+        <v>-3746.21</v>
       </c>
       <c r="E12">
-        <v>7126</v>
+        <v>153322400</v>
       </c>
       <c r="F12" t="s">
-        <v>84</v>
+        <v>99</v>
       </c>
       <c r="G12" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H12">
-        <v>0.1275</v>
+        <v>0.0007</v>
       </c>
       <c r="I12">
-        <v>908.5599999999999</v>
+        <v>107325.68</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13">
-        <v>3750</v>
+        <v>1109</v>
       </c>
       <c r="B13">
-        <v>4700</v>
+        <v>2000</v>
       </c>
       <c r="C13">
-        <v>628</v>
+        <v>32.86</v>
       </c>
       <c r="D13">
-        <v>-20968.81</v>
+        <v>-56.09</v>
       </c>
       <c r="E13">
-        <v>2951600</v>
+        <v>65720</v>
       </c>
       <c r="F13" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G13" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H13">
         <v>0.1275</v>
       </c>
       <c r="I13">
-        <v>376329</v>
+        <v>8379.299999999999</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14">
-        <v>388</v>
+        <v>1113</v>
       </c>
       <c r="B14">
-        <v>33000</v>
+        <v>20000</v>
       </c>
       <c r="C14">
-        <v>410</v>
+        <v>46.8</v>
       </c>
       <c r="D14">
-        <v>-19349.95</v>
+        <v>-3364.75</v>
       </c>
       <c r="E14">
-        <v>13530000</v>
+        <v>936000</v>
       </c>
       <c r="F14" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G14" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H14">
         <v>0.1275</v>
       </c>
       <c r="I14">
-        <v>1725075</v>
+        <v>119340</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15">
-        <v>3988</v>
+        <v>1258</v>
       </c>
       <c r="B15">
-        <v>4000</v>
+        <v>1000</v>
       </c>
       <c r="C15">
-        <v>5.28</v>
+        <v>15.96</v>
       </c>
       <c r="D15">
-        <v>5.1</v>
+        <v>-3.82</v>
       </c>
       <c r="E15">
-        <v>21120</v>
+        <v>15960</v>
       </c>
       <c r="F15" t="s">
-        <v>84</v>
+        <v>100</v>
       </c>
       <c r="G15" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H15">
         <v>0.1275</v>
       </c>
       <c r="I15">
-        <v>2692.8</v>
+        <v>2034.9</v>
       </c>
     </row>
     <row r="16" spans="1:9">
-      <c r="A16" t="s">
-        <v>9</v>
+      <c r="A16">
+        <v>1288</v>
       </c>
       <c r="B16">
-        <v>18000</v>
+        <v>6000</v>
       </c>
       <c r="C16">
-        <v>7403</v>
+        <v>5.935</v>
       </c>
       <c r="D16">
-        <v>27943.78</v>
+        <v>-3.82</v>
       </c>
       <c r="E16">
-        <v>133254000</v>
+        <v>35610</v>
       </c>
       <c r="F16" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G16" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H16">
-        <v>0.0063</v>
+        <v>0.1275</v>
       </c>
       <c r="I16">
-        <v>839500.2</v>
+        <v>4540.27</v>
       </c>
     </row>
     <row r="17" spans="1:9">
-      <c r="A17" t="s">
-        <v>10</v>
+      <c r="A17">
+        <v>1398</v>
       </c>
       <c r="B17">
-        <v>12000</v>
+        <v>1566000</v>
       </c>
       <c r="C17">
-        <v>7421</v>
+        <v>7.2</v>
       </c>
       <c r="D17">
-        <v>-30897.19</v>
+        <v>-998.09</v>
       </c>
       <c r="E17">
-        <v>89052000</v>
+        <v>11275200</v>
       </c>
       <c r="F17" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G17" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H17">
-        <v>0.0063</v>
+        <v>0.1275</v>
       </c>
       <c r="I17">
-        <v>561027.6</v>
+        <v>1437588</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18">
-        <v>700</v>
+        <v>1698</v>
       </c>
       <c r="B18">
+        <v>2000</v>
+      </c>
+      <c r="C18">
+        <v>37.4</v>
+      </c>
+      <c r="D18">
+        <v>-50.99</v>
+      </c>
+      <c r="E18">
+        <v>74800</v>
+      </c>
+      <c r="F18" t="s">
         <v>100</v>
       </c>
-      <c r="C18">
-        <v>479.2</v>
-      </c>
-      <c r="D18">
-        <v>-165.71</v>
-      </c>
-      <c r="E18">
-        <v>47920</v>
-      </c>
-      <c r="F18" t="s">
-        <v>84</v>
-      </c>
       <c r="G18" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H18">
         <v>0.1275</v>
       </c>
       <c r="I18">
-        <v>6109.8</v>
+        <v>9537</v>
       </c>
     </row>
     <row r="19" spans="1:9">
-      <c r="A19" t="s">
-        <v>11</v>
+      <c r="A19">
+        <v>1810</v>
       </c>
       <c r="B19">
-        <v>2600</v>
+        <v>200</v>
       </c>
       <c r="C19">
-        <v>7220</v>
+        <v>26.86</v>
       </c>
       <c r="D19">
-        <v>3445.64</v>
+        <v>-19.89</v>
       </c>
       <c r="E19">
-        <v>18772000</v>
+        <v>5372</v>
       </c>
       <c r="F19" t="s">
-        <v>85</v>
+        <v>100</v>
       </c>
       <c r="G19" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H19">
-        <v>0.0063</v>
+        <v>0.1275</v>
       </c>
       <c r="I19">
-        <v>118263.6</v>
+        <v>684.9299999999999</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20">
-        <v>9633</v>
+        <v>2207</v>
       </c>
       <c r="B20">
-        <v>1800</v>
+        <v>7000</v>
       </c>
       <c r="C20">
-        <v>42.46</v>
+        <v>516</v>
       </c>
       <c r="D20">
-        <v>100.96</v>
+        <v>1519.39</v>
       </c>
       <c r="E20">
-        <v>76428</v>
+        <v>3612000</v>
       </c>
       <c r="F20" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="G20" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H20">
+        <v>0.031</v>
+      </c>
+      <c r="I20">
+        <v>111972</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21">
+        <v>2318</v>
+      </c>
+      <c r="B21">
+        <v>16500</v>
+      </c>
+      <c r="C21">
+        <v>57.3</v>
+      </c>
+      <c r="D21">
+        <v>-1415</v>
+      </c>
+      <c r="E21">
+        <v>945450</v>
+      </c>
+      <c r="F21" t="s">
+        <v>100</v>
+      </c>
+      <c r="G21" t="s">
+        <v>106</v>
+      </c>
+      <c r="H21">
         <v>0.1275</v>
       </c>
-      <c r="I20">
-        <v>9744.57</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
-      <c r="A21" t="s">
-        <v>12</v>
-      </c>
-      <c r="B21">
-        <v>6000</v>
-      </c>
-      <c r="C21">
-        <v>2.53</v>
-      </c>
-      <c r="D21">
-        <v>-186.96</v>
-      </c>
-      <c r="E21">
-        <v>15180</v>
-      </c>
-      <c r="F21" t="s">
-        <v>86</v>
-      </c>
-      <c r="G21" t="s">
-        <v>88</v>
-      </c>
-      <c r="H21">
-        <v>0.779</v>
-      </c>
       <c r="I21">
-        <v>11825.22</v>
+        <v>120544.88</v>
       </c>
     </row>
     <row r="22" spans="1:9">
-      <c r="A22" t="s">
-        <v>13</v>
+      <c r="A22">
+        <v>2359</v>
       </c>
       <c r="B22">
-        <v>13900</v>
+        <v>300</v>
       </c>
       <c r="C22">
-        <v>108.18</v>
+        <v>179.7</v>
       </c>
       <c r="D22">
-        <v>1668</v>
+        <v>-145.32</v>
       </c>
       <c r="E22">
-        <v>1503702</v>
+        <v>53910</v>
       </c>
       <c r="F22" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G22" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H22">
-        <v>1</v>
+        <v>0.1275</v>
       </c>
       <c r="I22">
-        <v>1503702</v>
+        <v>6873.52</v>
       </c>
     </row>
     <row r="23" spans="1:9">
-      <c r="A23" t="s">
-        <v>14</v>
+      <c r="A23">
+        <v>267</v>
       </c>
       <c r="B23">
-        <v>10375</v>
+        <v>79000</v>
       </c>
       <c r="C23">
-        <v>91.67</v>
+        <v>11.94</v>
       </c>
       <c r="D23">
-        <v>-5291.25</v>
+        <v>-801.98</v>
       </c>
       <c r="E23">
-        <v>951076.25</v>
+        <v>943260</v>
       </c>
       <c r="F23" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G23" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H23">
-        <v>1</v>
+        <v>0.1275</v>
       </c>
       <c r="I23">
-        <v>951076.25</v>
+        <v>120265.65</v>
       </c>
     </row>
     <row r="24" spans="1:9">
-      <c r="A24" t="s">
-        <v>15</v>
+      <c r="A24">
+        <v>2800</v>
       </c>
       <c r="B24">
-        <v>10</v>
+        <v>2000</v>
       </c>
       <c r="C24">
-        <v>126.42</v>
+        <v>26</v>
       </c>
       <c r="D24">
-        <v>-8.199999999999999</v>
+        <v>-101.98</v>
       </c>
       <c r="E24">
-        <v>1264.2</v>
+        <v>52000</v>
       </c>
       <c r="F24" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G24" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H24">
-        <v>1</v>
+        <v>0.1275</v>
       </c>
       <c r="I24">
-        <v>1264.2</v>
+        <v>6630</v>
       </c>
     </row>
     <row r="25" spans="1:9">
-      <c r="A25" t="s">
-        <v>16</v>
+      <c r="A25">
+        <v>2828</v>
       </c>
       <c r="B25">
-        <v>7000</v>
+        <v>600</v>
       </c>
       <c r="C25">
-        <v>126.81</v>
+        <v>87.54000000000001</v>
       </c>
       <c r="D25">
-        <v>-12040</v>
+        <v>-76.48</v>
       </c>
       <c r="E25">
-        <v>887670</v>
+        <v>52524</v>
       </c>
       <c r="F25" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G25" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H25">
-        <v>1</v>
+        <v>0.1275</v>
       </c>
       <c r="I25">
-        <v>887670</v>
+        <v>6696.81</v>
       </c>
     </row>
     <row r="26" spans="1:9">
-      <c r="A26" t="s">
-        <v>17</v>
+      <c r="A26">
+        <v>2884</v>
       </c>
       <c r="B26">
-        <v>31000</v>
+        <v>102000</v>
       </c>
       <c r="C26">
-        <v>63</v>
+        <v>37.95</v>
       </c>
       <c r="D26">
-        <v>-7750</v>
+        <v>-474.42</v>
       </c>
       <c r="E26">
-        <v>1953000</v>
+        <v>3870900</v>
       </c>
       <c r="F26" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G26" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H26">
-        <v>1</v>
+        <v>0.031</v>
       </c>
       <c r="I26">
-        <v>1953000</v>
+        <v>119997.9</v>
       </c>
     </row>
     <row r="27" spans="1:9">
-      <c r="A27" t="s">
-        <v>18</v>
+      <c r="A27">
+        <v>2886</v>
       </c>
       <c r="B27">
-        <v>70</v>
+        <v>77000</v>
       </c>
       <c r="C27">
-        <v>18.3</v>
+        <v>50.3</v>
       </c>
       <c r="D27">
-        <v>-9.1</v>
+        <v>-2148.85</v>
       </c>
       <c r="E27">
-        <v>1281</v>
+        <v>3873100</v>
       </c>
       <c r="F27" t="s">
-        <v>87</v>
+        <v>101</v>
       </c>
       <c r="G27" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H27">
-        <v>1</v>
+        <v>0.031</v>
       </c>
       <c r="I27">
-        <v>1281</v>
+        <v>120066.1</v>
       </c>
     </row>
     <row r="28" spans="1:9">
-      <c r="A28" t="s">
-        <v>19</v>
+      <c r="A28">
+        <v>2899</v>
       </c>
       <c r="B28">
-        <v>3000</v>
+        <v>2000</v>
       </c>
       <c r="C28">
-        <v>11.16</v>
+        <v>35.3</v>
       </c>
       <c r="D28">
-        <v>-116.85</v>
+        <v>25.49</v>
       </c>
       <c r="E28">
-        <v>33480</v>
+        <v>70600</v>
       </c>
       <c r="F28" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="G28" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H28">
-        <v>0.779</v>
+        <v>0.1275</v>
       </c>
       <c r="I28">
-        <v>26080.92</v>
+        <v>9001.5</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B29">
-        <v>821</v>
+        <v>2600</v>
       </c>
       <c r="C29">
-        <v>166.7</v>
+        <v>7030</v>
       </c>
       <c r="D29">
-        <v>-1297.18</v>
+        <v>3363.6</v>
       </c>
       <c r="E29">
-        <v>136860.7</v>
+        <v>18278000</v>
       </c>
       <c r="F29" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G29" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H29">
-        <v>1</v>
+        <v>0.0063</v>
       </c>
       <c r="I29">
-        <v>136860.7</v>
+        <v>115151.4</v>
       </c>
     </row>
     <row r="30" spans="1:9">
-      <c r="A30" t="s">
-        <v>21</v>
+      <c r="A30">
+        <v>3</v>
       </c>
       <c r="B30">
-        <v>200</v>
+        <v>139000</v>
       </c>
       <c r="C30">
-        <v>7.7</v>
+        <v>6.785</v>
       </c>
       <c r="D30">
-        <v>1.56</v>
+        <v>-785.78</v>
       </c>
       <c r="E30">
-        <v>1540</v>
+        <v>943115</v>
       </c>
       <c r="F30" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="G30" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H30">
-        <v>0.779</v>
+        <v>0.1275</v>
       </c>
       <c r="I30">
-        <v>1199.66</v>
+        <v>120247.16</v>
       </c>
     </row>
     <row r="31" spans="1:9">
-      <c r="A31" t="s">
-        <v>22</v>
+      <c r="A31">
+        <v>3067</v>
       </c>
       <c r="B31">
-        <v>15</v>
+        <v>700</v>
       </c>
       <c r="C31">
-        <v>261.1</v>
+        <v>10.18</v>
       </c>
       <c r="D31">
-        <v>-60.3</v>
+        <v>-19.63</v>
       </c>
       <c r="E31">
-        <v>3916.5</v>
+        <v>7126</v>
       </c>
       <c r="F31" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G31" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H31">
-        <v>1</v>
+        <v>0.1275</v>
       </c>
       <c r="I31">
-        <v>3916.5</v>
+        <v>908.5599999999999</v>
       </c>
     </row>
     <row r="32" spans="1:9">
-      <c r="A32" t="s">
-        <v>23</v>
+      <c r="A32">
+        <v>3328</v>
       </c>
       <c r="B32">
-        <v>808799</v>
+        <v>129000</v>
       </c>
       <c r="C32">
-        <v>33.77</v>
+        <v>7.29</v>
       </c>
       <c r="D32">
-        <v>-273021.23</v>
+        <v>-732.9299999999999</v>
       </c>
       <c r="E32">
-        <v>27313142.23</v>
+        <v>940410</v>
       </c>
       <c r="F32" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G32" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H32">
-        <v>1</v>
+        <v>0.1275</v>
       </c>
       <c r="I32">
-        <v>27313142.23</v>
+        <v>119902.28</v>
       </c>
     </row>
     <row r="33" spans="1:9">
-      <c r="A33" t="s">
-        <v>24</v>
+      <c r="A33">
+        <v>3750</v>
       </c>
       <c r="B33">
-        <v>29</v>
+        <v>4700</v>
       </c>
       <c r="C33">
-        <v>264.32</v>
+        <v>628</v>
       </c>
       <c r="D33">
-        <v>-13.34</v>
+        <v>-20968.81</v>
       </c>
       <c r="E33">
-        <v>7665.28</v>
+        <v>2951600</v>
       </c>
       <c r="F33" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G33" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H33">
-        <v>1</v>
+        <v>0.1275</v>
       </c>
       <c r="I33">
-        <v>7665.28</v>
+        <v>376329</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="B34">
-        <v>98183</v>
+        <v>1564</v>
       </c>
       <c r="C34">
-        <v>50.64</v>
+        <v>41800</v>
       </c>
       <c r="D34">
-        <v>41236.86</v>
+        <v>274.73</v>
       </c>
       <c r="E34">
-        <v>4971987.12</v>
+        <v>65375200</v>
       </c>
       <c r="F34" t="s">
-        <v>87</v>
+        <v>99</v>
       </c>
       <c r="G34" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H34">
-        <v>1</v>
+        <v>0.0007</v>
       </c>
       <c r="I34">
-        <v>4971987.12</v>
+        <v>45762.64</v>
       </c>
     </row>
     <row r="35" spans="1:9">
-      <c r="A35" t="s">
-        <v>26</v>
+      <c r="A35">
+        <v>386</v>
       </c>
       <c r="B35">
+        <v>220000</v>
+      </c>
+      <c r="C35">
+        <v>4.265</v>
+      </c>
+      <c r="D35">
+        <v>-1659.43</v>
+      </c>
+      <c r="E35">
+        <v>938300</v>
+      </c>
+      <c r="F35" t="s">
+        <v>100</v>
+      </c>
+      <c r="G35" t="s">
+        <v>106</v>
+      </c>
+      <c r="H35">
+        <v>0.1275</v>
+      </c>
+      <c r="I35">
+        <v>119633.25</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36">
+        <v>388</v>
+      </c>
+      <c r="B36">
+        <v>35300</v>
+      </c>
+      <c r="C36">
+        <v>410</v>
+      </c>
+      <c r="D36">
+        <v>-20620.38</v>
+      </c>
+      <c r="E36">
+        <v>14473000</v>
+      </c>
+      <c r="F36" t="s">
+        <v>100</v>
+      </c>
+      <c r="G36" t="s">
+        <v>106</v>
+      </c>
+      <c r="H36">
+        <v>0.1275</v>
+      </c>
+      <c r="I36">
+        <v>1845307.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37">
+        <v>3968</v>
+      </c>
+      <c r="B37">
+        <v>19000</v>
+      </c>
+      <c r="C37">
+        <v>48.9</v>
+      </c>
+      <c r="D37">
+        <v>330.64</v>
+      </c>
+      <c r="E37">
+        <v>929100</v>
+      </c>
+      <c r="F37" t="s">
+        <v>100</v>
+      </c>
+      <c r="G37" t="s">
+        <v>106</v>
+      </c>
+      <c r="H37">
+        <v>0.1275</v>
+      </c>
+      <c r="I37">
+        <v>118460.25</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38">
+        <v>3988</v>
+      </c>
+      <c r="B38">
+        <v>4000</v>
+      </c>
+      <c r="C38">
+        <v>5.28</v>
+      </c>
+      <c r="D38">
+        <v>5.1</v>
+      </c>
+      <c r="E38">
+        <v>21120</v>
+      </c>
+      <c r="F38" t="s">
+        <v>100</v>
+      </c>
+      <c r="G38" t="s">
+        <v>106</v>
+      </c>
+      <c r="H38">
+        <v>0.1275</v>
+      </c>
+      <c r="I38">
+        <v>2692.8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39">
         <v>5</v>
       </c>
-      <c r="C35">
-        <v>145.41</v>
-      </c>
-      <c r="D35">
-        <v>-22.4</v>
-      </c>
-      <c r="E35">
-        <v>727.05</v>
-      </c>
-      <c r="F35" t="s">
-        <v>87</v>
-      </c>
-      <c r="G35" t="s">
-        <v>88</v>
-      </c>
-      <c r="H35">
-        <v>1</v>
-      </c>
-      <c r="I35">
-        <v>727.05</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
-      <c r="A36" t="s">
-        <v>27</v>
-      </c>
-      <c r="B36">
-        <v>-2700</v>
-      </c>
-      <c r="C36">
-        <v>207.39</v>
-      </c>
-      <c r="D36">
-        <v>6669</v>
-      </c>
-      <c r="E36">
-        <v>-559953</v>
-      </c>
-      <c r="F36" t="s">
-        <v>87</v>
-      </c>
-      <c r="G36" t="s">
-        <v>88</v>
-      </c>
-      <c r="H36">
-        <v>1</v>
-      </c>
-      <c r="I36">
-        <v>-559953</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
-      <c r="A37" t="s">
-        <v>28</v>
-      </c>
-      <c r="B37">
-        <v>13</v>
-      </c>
-      <c r="C37">
-        <v>120.88</v>
-      </c>
-      <c r="D37">
-        <v>-8.06</v>
-      </c>
-      <c r="E37">
-        <v>1571.44</v>
-      </c>
-      <c r="F37" t="s">
-        <v>87</v>
-      </c>
-      <c r="G37" t="s">
-        <v>88</v>
-      </c>
-      <c r="H37">
-        <v>1</v>
-      </c>
-      <c r="I37">
-        <v>1571.44</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
-      <c r="A38" t="s">
-        <v>29</v>
-      </c>
-      <c r="B38">
-        <v>10</v>
-      </c>
-      <c r="C38">
-        <v>202.15</v>
-      </c>
-      <c r="D38">
-        <v>7.5</v>
-      </c>
-      <c r="E38">
-        <v>2021.5</v>
-      </c>
-      <c r="F38" t="s">
-        <v>87</v>
-      </c>
-      <c r="G38" t="s">
-        <v>88</v>
-      </c>
-      <c r="H38">
-        <v>1</v>
-      </c>
-      <c r="I38">
-        <v>2021.5</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
-      <c r="A39" t="s">
-        <v>30</v>
-      </c>
       <c r="B39">
-        <v>800</v>
+        <v>5600</v>
       </c>
       <c r="C39">
-        <v>75.08</v>
+        <v>160.1</v>
       </c>
       <c r="D39">
-        <v>953.52</v>
+        <v>-1427.66</v>
       </c>
       <c r="E39">
-        <v>60064</v>
+        <v>896560</v>
       </c>
       <c r="F39" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="G39" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H39">
-        <v>0.779</v>
+        <v>0.1275</v>
       </c>
       <c r="I39">
-        <v>46789.86</v>
+        <v>114311.4</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B40">
-        <v>523026</v>
+        <v>18000</v>
       </c>
       <c r="C40">
-        <v>30.94</v>
+        <v>7403</v>
       </c>
       <c r="D40">
-        <v>125526.24</v>
+        <v>27943.78</v>
       </c>
       <c r="E40">
-        <v>16182424.44</v>
+        <v>133254000</v>
       </c>
       <c r="F40" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G40" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H40">
-        <v>1</v>
+        <v>0.0063</v>
       </c>
       <c r="I40">
-        <v>16182424.44</v>
+        <v>839500.2</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B41">
-        <v>-2000</v>
+        <v>12000</v>
       </c>
       <c r="C41">
-        <v>229.29</v>
+        <v>7421</v>
       </c>
       <c r="D41">
-        <v>107760</v>
+        <v>-30897.19</v>
       </c>
       <c r="E41">
-        <v>-458580</v>
+        <v>89052000</v>
       </c>
       <c r="F41" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G41" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H41">
-        <v>1</v>
+        <v>0.0063</v>
       </c>
       <c r="I41">
-        <v>-458580</v>
+        <v>561027.6</v>
       </c>
     </row>
     <row r="42" spans="1:9">
-      <c r="A42" t="s">
-        <v>33</v>
+      <c r="A42">
+        <v>700</v>
       </c>
       <c r="B42">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="C42">
-        <v>127.45</v>
+        <v>479.2</v>
       </c>
       <c r="D42">
-        <v>2550</v>
+        <v>-165.71</v>
       </c>
       <c r="E42">
-        <v>637250</v>
+        <v>47920</v>
       </c>
       <c r="F42" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G42" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H42">
-        <v>1</v>
+        <v>0.1275</v>
       </c>
       <c r="I42">
-        <v>637250</v>
+        <v>6109.8</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="B43">
-        <v>1</v>
+        <v>2600</v>
       </c>
       <c r="C43">
-        <v>107.36</v>
+        <v>7220</v>
       </c>
       <c r="D43">
-        <v>-0.07000000000000001</v>
+        <v>3445.64</v>
       </c>
       <c r="E43">
-        <v>107.36</v>
+        <v>18772000</v>
       </c>
       <c r="F43" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="G43" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H43">
-        <v>1</v>
+        <v>0.0063</v>
       </c>
       <c r="I43">
-        <v>107.36</v>
+        <v>118263.6</v>
       </c>
     </row>
     <row r="44" spans="1:9">
-      <c r="A44" t="s">
-        <v>35</v>
+      <c r="A44">
+        <v>941</v>
       </c>
       <c r="B44">
-        <v>36</v>
+        <v>11000</v>
       </c>
       <c r="C44">
-        <v>156.91</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="D44">
-        <v>-200.16</v>
+        <v>-420.65</v>
       </c>
       <c r="E44">
-        <v>5648.76</v>
+        <v>906400</v>
       </c>
       <c r="F44" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G44" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H44">
-        <v>1</v>
+        <v>0.1275</v>
       </c>
       <c r="I44">
-        <v>5648.76</v>
+        <v>115566</v>
       </c>
     </row>
     <row r="45" spans="1:9">
-      <c r="A45" t="s">
-        <v>36</v>
+      <c r="A45">
+        <v>9633</v>
       </c>
       <c r="B45">
-        <v>17</v>
+        <v>1800</v>
       </c>
       <c r="C45">
-        <v>448.19</v>
+        <v>42.46</v>
       </c>
       <c r="D45">
-        <v>15.47</v>
+        <v>100.96</v>
       </c>
       <c r="E45">
-        <v>7619.23</v>
+        <v>76428</v>
       </c>
       <c r="F45" t="s">
-        <v>87</v>
+        <v>100</v>
       </c>
       <c r="G45" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H45">
-        <v>1</v>
+        <v>0.1275</v>
       </c>
       <c r="I45">
-        <v>7619.23</v>
+        <v>9744.57</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>37</v>
+        <v>23</v>
       </c>
       <c r="B46">
-        <v>27000</v>
+        <v>6000</v>
       </c>
       <c r="C46">
-        <v>164.12</v>
+        <v>2.53</v>
       </c>
       <c r="D46">
-        <v>-135540</v>
+        <v>-186.96</v>
       </c>
       <c r="E46">
-        <v>4431240</v>
+        <v>15180</v>
       </c>
       <c r="F46" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G46" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H46">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I46">
-        <v>4431240</v>
+        <v>11825.22</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="B47">
-        <v>62</v>
+        <v>13900</v>
       </c>
       <c r="C47">
-        <v>1000.3</v>
+        <v>108.18</v>
       </c>
       <c r="D47">
-        <v>-1094.92</v>
+        <v>1668</v>
       </c>
       <c r="E47">
-        <v>62018.6</v>
+        <v>1503702</v>
       </c>
       <c r="F47" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G47" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H47">
         <v>1</v>
       </c>
       <c r="I47">
-        <v>62018.6</v>
+        <v>1503702</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="B48">
-        <v>6400</v>
+        <v>10375</v>
       </c>
       <c r="C48">
-        <v>84.03</v>
+        <v>91.67</v>
       </c>
       <c r="D48">
-        <v>0</v>
+        <v>-5291.25</v>
       </c>
       <c r="E48">
-        <v>537792</v>
+        <v>951076.25</v>
       </c>
       <c r="F48" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G48" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H48">
         <v>1</v>
       </c>
       <c r="I48">
-        <v>537792</v>
+        <v>951076.25</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>40</v>
+        <v>26</v>
       </c>
       <c r="B49">
-        <v>2160</v>
+        <v>10</v>
       </c>
       <c r="C49">
-        <v>357.75</v>
+        <v>126.42</v>
       </c>
       <c r="D49">
-        <v>-10108.8</v>
+        <v>-8.199999999999999</v>
       </c>
       <c r="E49">
-        <v>772740</v>
+        <v>1264.2</v>
       </c>
       <c r="F49" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G49" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H49">
         <v>1</v>
       </c>
       <c r="I49">
-        <v>772740</v>
+        <v>1264.2</v>
       </c>
     </row>
     <row r="50" spans="1:9">
       <c r="A50" t="s">
-        <v>41</v>
+        <v>27</v>
       </c>
       <c r="B50">
-        <v>118000</v>
+        <v>7000</v>
       </c>
       <c r="C50">
-        <v>32.35</v>
+        <v>126.81</v>
       </c>
       <c r="D50">
-        <v>51920</v>
+        <v>-12040</v>
       </c>
       <c r="E50">
-        <v>3817300</v>
+        <v>887670</v>
       </c>
       <c r="F50" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G50" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H50">
         <v>1</v>
       </c>
       <c r="I50">
-        <v>3817300</v>
+        <v>887670</v>
       </c>
     </row>
     <row r="51" spans="1:9">
       <c r="A51" t="s">
-        <v>42</v>
+        <v>28</v>
       </c>
       <c r="B51">
-        <v>42</v>
+        <v>31000</v>
       </c>
       <c r="C51">
-        <v>149.75</v>
+        <v>63</v>
       </c>
       <c r="D51">
-        <v>-3.78</v>
+        <v>-7750</v>
       </c>
       <c r="E51">
-        <v>6289.5</v>
+        <v>1953000</v>
       </c>
       <c r="F51" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G51" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H51">
         <v>1</v>
       </c>
       <c r="I51">
-        <v>6289.5</v>
+        <v>1953000</v>
       </c>
     </row>
     <row r="52" spans="1:9">
       <c r="A52" t="s">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="B52">
-        <v>430000</v>
+        <v>70</v>
       </c>
       <c r="C52">
-        <v>24.18</v>
+        <v>18.3</v>
       </c>
       <c r="D52">
-        <v>-38700</v>
+        <v>-9.1</v>
       </c>
       <c r="E52">
-        <v>10397400</v>
+        <v>1281</v>
       </c>
       <c r="F52" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G52" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H52">
         <v>1</v>
       </c>
       <c r="I52">
-        <v>10397400</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="53" spans="1:9">
       <c r="A53" t="s">
-        <v>44</v>
+        <v>30</v>
       </c>
       <c r="B53">
-        <v>8500</v>
+        <v>3000</v>
       </c>
       <c r="C53">
-        <v>356.3</v>
+        <v>11.16</v>
       </c>
       <c r="D53">
-        <v>-24990</v>
+        <v>-116.85</v>
       </c>
       <c r="E53">
-        <v>3028550</v>
+        <v>33480</v>
       </c>
       <c r="F53" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G53" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H53">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I53">
-        <v>3028550</v>
+        <v>26080.92</v>
       </c>
     </row>
     <row r="54" spans="1:9">
       <c r="A54" t="s">
-        <v>45</v>
+        <v>31</v>
       </c>
       <c r="B54">
-        <v>333</v>
+        <v>821</v>
       </c>
       <c r="C54">
-        <v>0.89</v>
+        <v>166.7</v>
       </c>
       <c r="D54">
-        <v>-1.3</v>
+        <v>-1297.18</v>
       </c>
       <c r="E54">
-        <v>296.37</v>
+        <v>136860.7</v>
       </c>
       <c r="F54" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="G54" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H54">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="I54">
-        <v>230.87</v>
+        <v>136860.7</v>
       </c>
     </row>
     <row r="55" spans="1:9">
       <c r="A55" t="s">
-        <v>46</v>
+        <v>32</v>
       </c>
       <c r="B55">
-        <v>874744</v>
+        <v>200</v>
       </c>
       <c r="C55">
-        <v>28.61</v>
+        <v>7.7</v>
       </c>
       <c r="D55">
-        <v>201191.12</v>
+        <v>1.56</v>
       </c>
       <c r="E55">
-        <v>25026425.84</v>
+        <v>1540</v>
       </c>
       <c r="F55" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G55" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H55">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I55">
-        <v>25026425.84</v>
+        <v>1199.66</v>
       </c>
     </row>
     <row r="56" spans="1:9">
       <c r="A56" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
       <c r="B56">
-        <v>53200</v>
+        <v>15</v>
       </c>
       <c r="C56">
-        <v>16.81</v>
+        <v>261.1</v>
       </c>
       <c r="D56">
-        <v>-86716</v>
+        <v>-60.3</v>
       </c>
       <c r="E56">
-        <v>894292</v>
+        <v>3916.5</v>
       </c>
       <c r="F56" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G56" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H56">
         <v>1</v>
       </c>
       <c r="I56">
-        <v>894292</v>
+        <v>3916.5</v>
       </c>
     </row>
     <row r="57" spans="1:9">
       <c r="A57" t="s">
-        <v>48</v>
+        <v>34</v>
       </c>
       <c r="B57">
-        <v>39851</v>
+        <v>808799</v>
       </c>
       <c r="C57">
-        <v>76.48999999999999</v>
+        <v>33.77</v>
       </c>
       <c r="D57">
-        <v>-33873.35</v>
+        <v>-273021.23</v>
       </c>
       <c r="E57">
-        <v>3048202.99</v>
+        <v>27313142.23</v>
       </c>
       <c r="F57" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G57" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H57">
         <v>1</v>
       </c>
       <c r="I57">
-        <v>3048202.99</v>
+        <v>27313142.23</v>
       </c>
     </row>
     <row r="58" spans="1:9">
       <c r="A58" t="s">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="B58">
-        <v>1794</v>
+        <v>29</v>
       </c>
       <c r="C58">
-        <v>3.02</v>
+        <v>264.32</v>
       </c>
       <c r="D58">
-        <v>-125.58</v>
+        <v>-13.34</v>
       </c>
       <c r="E58">
-        <v>5417.88</v>
+        <v>7665.28</v>
       </c>
       <c r="F58" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G58" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H58">
         <v>1</v>
       </c>
       <c r="I58">
-        <v>5417.88</v>
+        <v>7665.28</v>
       </c>
     </row>
     <row r="59" spans="1:9">
       <c r="A59" t="s">
-        <v>50</v>
+        <v>36</v>
       </c>
       <c r="B59">
-        <v>3</v>
+        <v>98183</v>
       </c>
       <c r="C59">
-        <v>1191.94</v>
+        <v>50.64</v>
       </c>
       <c r="D59">
-        <v>66.23999999999999</v>
+        <v>41236.86</v>
       </c>
       <c r="E59">
-        <v>3575.82</v>
+        <v>4971987.12</v>
       </c>
       <c r="F59" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G59" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H59">
         <v>1</v>
       </c>
       <c r="I59">
-        <v>3575.82</v>
+        <v>4971987.12</v>
       </c>
     </row>
     <row r="60" spans="1:9">
       <c r="A60" t="s">
-        <v>51</v>
+        <v>37</v>
       </c>
       <c r="B60">
-        <v>8000</v>
+        <v>5</v>
       </c>
       <c r="C60">
-        <v>1.93</v>
+        <v>145.41</v>
       </c>
       <c r="D60">
-        <v>-62.32</v>
+        <v>-22.4</v>
       </c>
       <c r="E60">
-        <v>15440</v>
+        <v>727.05</v>
       </c>
       <c r="F60" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="G60" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H60">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="I60">
-        <v>12027.76</v>
+        <v>727.05</v>
       </c>
     </row>
     <row r="61" spans="1:9">
       <c r="A61" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="B61">
-        <v>787</v>
+        <v>-2700</v>
       </c>
       <c r="C61">
-        <v>567.74</v>
+        <v>207.39</v>
       </c>
       <c r="D61">
-        <v>8082.49</v>
+        <v>6669</v>
       </c>
       <c r="E61">
-        <v>446811.38</v>
+        <v>-559953</v>
       </c>
       <c r="F61" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G61" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H61">
         <v>1</v>
       </c>
       <c r="I61">
-        <v>446811.38</v>
+        <v>-559953</v>
       </c>
     </row>
     <row r="62" spans="1:9">
       <c r="A62" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="B62">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="C62">
-        <v>45.97</v>
+        <v>120.88</v>
       </c>
       <c r="D62">
-        <v>72</v>
+        <v>-8.06</v>
       </c>
       <c r="E62">
-        <v>2298.5</v>
+        <v>1571.44</v>
       </c>
       <c r="F62" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G62" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H62">
         <v>1</v>
       </c>
       <c r="I62">
-        <v>2298.5</v>
+        <v>1571.44</v>
       </c>
     </row>
     <row r="63" spans="1:9">
       <c r="A63" t="s">
-        <v>54</v>
+        <v>40</v>
       </c>
       <c r="B63">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="C63">
-        <v>62.36</v>
+        <v>202.15</v>
       </c>
       <c r="D63">
-        <v>-34</v>
+        <v>7.5</v>
       </c>
       <c r="E63">
-        <v>6236</v>
+        <v>2021.5</v>
       </c>
       <c r="F63" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G63" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H63">
         <v>1</v>
       </c>
       <c r="I63">
-        <v>6236</v>
+        <v>2021.5</v>
       </c>
     </row>
     <row r="64" spans="1:9">
       <c r="A64" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
       <c r="B64">
-        <v>34</v>
+        <v>630</v>
       </c>
       <c r="C64">
-        <v>359.49</v>
+        <v>189.23</v>
       </c>
       <c r="D64">
-        <v>-107.78</v>
+        <v>1776.6</v>
       </c>
       <c r="E64">
-        <v>12222.66</v>
+        <v>119214.9</v>
       </c>
       <c r="F64" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G64" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H64">
         <v>1</v>
       </c>
       <c r="I64">
-        <v>12222.66</v>
+        <v>119214.9</v>
       </c>
     </row>
     <row r="65" spans="1:9">
       <c r="A65" t="s">
-        <v>56</v>
+        <v>42</v>
       </c>
       <c r="B65">
-        <v>10</v>
+        <v>2800</v>
       </c>
       <c r="C65">
-        <v>103.92</v>
+        <v>75.08</v>
       </c>
       <c r="D65">
-        <v>-13.4</v>
+        <v>3337.32</v>
       </c>
       <c r="E65">
-        <v>1039.2</v>
+        <v>210224</v>
       </c>
       <c r="F65" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G65" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H65">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I65">
-        <v>1039.2</v>
+        <v>163764.5</v>
       </c>
     </row>
     <row r="66" spans="1:9">
       <c r="A66" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="B66">
-        <v>45900</v>
+        <v>523026</v>
       </c>
       <c r="C66">
-        <v>714.65</v>
+        <v>30.94</v>
       </c>
       <c r="D66">
-        <v>-121635</v>
+        <v>125526.24</v>
       </c>
       <c r="E66">
-        <v>32802435</v>
+        <v>16182424.44</v>
       </c>
       <c r="F66" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G66" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H66">
         <v>1</v>
       </c>
       <c r="I66">
-        <v>32802435</v>
+        <v>16182424.44</v>
       </c>
     </row>
     <row r="67" spans="1:9">
       <c r="A67" t="s">
-        <v>58</v>
+        <v>44</v>
       </c>
       <c r="B67">
-        <v>54654</v>
+        <v>-2000</v>
       </c>
       <c r="C67">
-        <v>294.26</v>
+        <v>229.29</v>
       </c>
       <c r="D67">
-        <v>-59572.86</v>
+        <v>107760</v>
       </c>
       <c r="E67">
-        <v>16082486.04</v>
+        <v>-458580</v>
       </c>
       <c r="F67" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G67" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H67">
         <v>1</v>
       </c>
       <c r="I67">
-        <v>16082486.04</v>
+        <v>-458580</v>
       </c>
     </row>
     <row r="68" spans="1:9">
       <c r="A68" t="s">
-        <v>59</v>
+        <v>45</v>
       </c>
       <c r="B68">
-        <v>4320</v>
+        <v>5000</v>
       </c>
       <c r="C68">
-        <v>223.25</v>
+        <v>127.45</v>
       </c>
       <c r="D68">
-        <v>4060.8</v>
+        <v>2550</v>
       </c>
       <c r="E68">
-        <v>964440</v>
+        <v>637250</v>
       </c>
       <c r="F68" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G68" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H68">
         <v>1</v>
       </c>
       <c r="I68">
-        <v>964440</v>
+        <v>637250</v>
       </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69" t="s">
-        <v>60</v>
+        <v>46</v>
       </c>
       <c r="B69">
-        <v>76900</v>
+        <v>1</v>
       </c>
       <c r="C69">
-        <v>24.32</v>
+        <v>107.36</v>
       </c>
       <c r="D69">
-        <v>18571.06</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E69">
-        <v>1870208</v>
+        <v>107.36</v>
       </c>
       <c r="F69" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="G69" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H69">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="I69">
-        <v>1456892.03</v>
+        <v>107.36</v>
       </c>
     </row>
     <row r="70" spans="1:9">
       <c r="A70" t="s">
-        <v>61</v>
+        <v>47</v>
       </c>
       <c r="B70">
-        <v>718033</v>
+        <v>36</v>
       </c>
       <c r="C70">
-        <v>33.7</v>
+        <v>156.91</v>
       </c>
       <c r="D70">
-        <v>43081.98</v>
+        <v>-200.16</v>
       </c>
       <c r="E70">
-        <v>24197712.1</v>
+        <v>5648.76</v>
       </c>
       <c r="F70" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G70" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H70">
         <v>1</v>
       </c>
       <c r="I70">
-        <v>24197712.1</v>
+        <v>5648.76</v>
       </c>
     </row>
     <row r="71" spans="1:9">
       <c r="A71" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="B71">
-        <v>8200</v>
+        <v>17</v>
       </c>
       <c r="C71">
-        <v>108.5923</v>
+        <v>448.19</v>
       </c>
       <c r="D71">
-        <v>-145.14</v>
+        <v>15.47</v>
       </c>
       <c r="E71">
-        <v>890456.86</v>
+        <v>7619.23</v>
       </c>
       <c r="F71" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G71" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H71">
         <v>1</v>
       </c>
       <c r="I71">
-        <v>890456.86</v>
+        <v>7619.23</v>
       </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72" t="s">
-        <v>63</v>
+        <v>49</v>
       </c>
       <c r="B72">
-        <v>100</v>
+        <v>5252</v>
       </c>
       <c r="C72">
-        <v>67.78</v>
+        <v>22.49</v>
       </c>
       <c r="D72">
-        <v>41</v>
+        <v>-735.28</v>
       </c>
       <c r="E72">
-        <v>6778</v>
+        <v>118117.48</v>
       </c>
       <c r="F72" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G72" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H72">
         <v>1</v>
       </c>
       <c r="I72">
-        <v>6778</v>
+        <v>118117.48</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73" t="s">
-        <v>64</v>
+        <v>50</v>
       </c>
       <c r="B73">
-        <v>20100</v>
+        <v>27000</v>
       </c>
       <c r="C73">
-        <v>2.27</v>
+        <v>164.12</v>
       </c>
       <c r="D73">
-        <v>402</v>
+        <v>-135540</v>
       </c>
       <c r="E73">
-        <v>45627</v>
+        <v>4431240</v>
       </c>
       <c r="F73" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G73" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H73">
         <v>1</v>
       </c>
       <c r="I73">
-        <v>45627</v>
+        <v>4431240</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74" t="s">
-        <v>65</v>
+        <v>51</v>
       </c>
       <c r="B74">
-        <v>18000</v>
+        <v>62</v>
       </c>
       <c r="C74">
-        <v>571.48</v>
+        <v>1000.3</v>
       </c>
       <c r="D74">
-        <v>32040</v>
+        <v>-1094.92</v>
       </c>
       <c r="E74">
-        <v>10286640</v>
+        <v>62018.6</v>
       </c>
       <c r="F74" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G74" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H74">
         <v>1</v>
       </c>
       <c r="I74">
-        <v>10286640</v>
+        <v>62018.6</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
       <c r="B75">
-        <v>15</v>
+        <v>6400</v>
       </c>
       <c r="C75">
-        <v>149.1</v>
+        <v>84.03</v>
       </c>
       <c r="D75">
-        <v>-17.55</v>
+        <v>0</v>
       </c>
       <c r="E75">
-        <v>2236.5</v>
+        <v>537792</v>
       </c>
       <c r="F75" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G75" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H75">
         <v>1</v>
       </c>
       <c r="I75">
-        <v>2236.5</v>
+        <v>537792</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76" t="s">
-        <v>67</v>
+        <v>53</v>
       </c>
       <c r="B76">
-        <v>2</v>
+        <v>2160</v>
       </c>
       <c r="C76">
-        <v>291.2</v>
+        <v>357.75</v>
       </c>
       <c r="D76">
-        <v>-3.3</v>
+        <v>-10108.8</v>
       </c>
       <c r="E76">
-        <v>582.4</v>
+        <v>772740</v>
       </c>
       <c r="F76" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G76" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H76">
         <v>1</v>
       </c>
       <c r="I76">
-        <v>582.4</v>
+        <v>772740</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77" t="s">
-        <v>68</v>
+        <v>54</v>
       </c>
       <c r="B77">
-        <v>87087</v>
+        <v>118000</v>
       </c>
       <c r="C77">
-        <v>72.03</v>
+        <v>32.35</v>
       </c>
       <c r="D77">
-        <v>-70540.47</v>
+        <v>51920</v>
       </c>
       <c r="E77">
-        <v>6272876.61</v>
+        <v>3817300</v>
       </c>
       <c r="F77" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G77" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H77">
         <v>1</v>
       </c>
       <c r="I77">
-        <v>6272876.61</v>
+        <v>3817300</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78" t="s">
-        <v>69</v>
+        <v>55</v>
       </c>
       <c r="B78">
-        <v>150200</v>
+        <v>42</v>
       </c>
       <c r="C78">
-        <v>43.58</v>
+        <v>149.75</v>
       </c>
       <c r="D78">
-        <v>60844.58</v>
+        <v>-3.78</v>
       </c>
       <c r="E78">
-        <v>6545716</v>
+        <v>6289.5</v>
       </c>
       <c r="F78" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="G78" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H78">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="I78">
-        <v>5099112.76</v>
+        <v>6289.5</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79" t="s">
-        <v>70</v>
+        <v>56</v>
       </c>
       <c r="B79">
-        <v>534400</v>
+        <v>430000</v>
       </c>
       <c r="C79">
-        <v>5.59</v>
+        <v>24.18</v>
       </c>
       <c r="D79">
-        <v>-8326.17</v>
+        <v>-38700</v>
       </c>
       <c r="E79">
-        <v>2987296</v>
+        <v>10397400</v>
       </c>
       <c r="F79" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="G79" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H79">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="I79">
-        <v>2327103.58</v>
+        <v>10397400</v>
       </c>
     </row>
     <row r="80" spans="1:9">
       <c r="A80" t="s">
-        <v>71</v>
+        <v>57</v>
       </c>
       <c r="B80">
-        <v>1</v>
+        <v>8500</v>
       </c>
       <c r="C80">
-        <v>100</v>
+        <v>356.3</v>
       </c>
       <c r="D80">
-        <v>0.31</v>
+        <v>-24990</v>
       </c>
       <c r="E80">
-        <v>100</v>
+        <v>3028550</v>
       </c>
       <c r="F80" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G80" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H80">
         <v>1</v>
       </c>
       <c r="I80">
-        <v>100</v>
+        <v>3028550</v>
       </c>
     </row>
     <row r="81" spans="1:9">
       <c r="A81" t="s">
-        <v>72</v>
+        <v>58</v>
       </c>
       <c r="B81">
-        <v>10</v>
+        <v>333</v>
       </c>
       <c r="C81">
-        <v>164.12</v>
+        <v>0.89</v>
       </c>
       <c r="D81">
-        <v>25.5</v>
+        <v>-1.3</v>
       </c>
       <c r="E81">
-        <v>1641.2</v>
+        <v>296.37</v>
       </c>
       <c r="F81" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G81" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H81">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I81">
-        <v>1641.2</v>
+        <v>230.87</v>
       </c>
     </row>
     <row r="82" spans="1:9">
       <c r="A82" t="s">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="B82">
-        <v>1000</v>
+        <v>874744</v>
       </c>
       <c r="C82">
-        <v>24.01</v>
+        <v>28.61</v>
       </c>
       <c r="D82">
-        <v>-159.9</v>
+        <v>201191.12</v>
       </c>
       <c r="E82">
-        <v>24010</v>
+        <v>25026425.84</v>
       </c>
       <c r="F82" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G82" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H82">
         <v>1</v>
       </c>
       <c r="I82">
-        <v>24010</v>
+        <v>25026425.84</v>
       </c>
     </row>
     <row r="83" spans="1:9">
       <c r="A83" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="B83">
-        <v>21</v>
+        <v>53200</v>
       </c>
       <c r="C83">
-        <v>275.17</v>
+        <v>16.81</v>
       </c>
       <c r="D83">
-        <v>-58.17</v>
+        <v>-86716</v>
       </c>
       <c r="E83">
-        <v>5778.57</v>
+        <v>894292</v>
       </c>
       <c r="F83" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G83" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H83">
         <v>1</v>
       </c>
       <c r="I83">
-        <v>5778.57</v>
+        <v>894292</v>
       </c>
     </row>
     <row r="84" spans="1:9">
       <c r="A84" t="s">
-        <v>75</v>
+        <v>61</v>
       </c>
       <c r="B84">
-        <v>10</v>
+        <v>39851</v>
       </c>
       <c r="C84">
-        <v>141.38</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="D84">
-        <v>8</v>
+        <v>-33873.35</v>
       </c>
       <c r="E84">
-        <v>1413.8</v>
+        <v>3048202.99</v>
       </c>
       <c r="F84" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G84" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H84">
         <v>1</v>
       </c>
       <c r="I84">
-        <v>1413.8</v>
+        <v>3048202.99</v>
       </c>
     </row>
     <row r="85" spans="1:9">
       <c r="A85" t="s">
-        <v>76</v>
+        <v>62</v>
       </c>
       <c r="B85">
-        <v>105000</v>
+        <v>1794</v>
       </c>
       <c r="C85">
-        <v>164.77</v>
+        <v>3.02</v>
       </c>
       <c r="D85">
-        <v>-37800</v>
+        <v>-125.58</v>
       </c>
       <c r="E85">
-        <v>17300850</v>
+        <v>5417.88</v>
       </c>
       <c r="F85" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G85" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H85">
         <v>1</v>
       </c>
       <c r="I85">
-        <v>17300850</v>
+        <v>5417.88</v>
       </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86" t="s">
-        <v>77</v>
+        <v>63</v>
       </c>
       <c r="B86">
-        <v>6003</v>
+        <v>3</v>
       </c>
       <c r="C86">
-        <v>46.99</v>
+        <v>1191.94</v>
       </c>
       <c r="D86">
-        <v>3121.56</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="E86">
-        <v>282080.97</v>
+        <v>3575.82</v>
       </c>
       <c r="F86" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G86" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H86">
         <v>1</v>
       </c>
       <c r="I86">
-        <v>282080.97</v>
+        <v>3575.82</v>
       </c>
     </row>
     <row r="87" spans="1:9">
       <c r="A87" t="s">
-        <v>78</v>
+        <v>64</v>
       </c>
       <c r="B87">
-        <v>28600</v>
+        <v>8000</v>
       </c>
       <c r="C87">
-        <v>85.11</v>
+        <v>1.93</v>
       </c>
       <c r="D87">
-        <v>-6292</v>
+        <v>-62.32</v>
       </c>
       <c r="E87">
-        <v>2434146</v>
+        <v>15440</v>
       </c>
       <c r="F87" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G87" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H87">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I87">
-        <v>2434146</v>
+        <v>12027.76</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88" t="s">
-        <v>79</v>
+        <v>65</v>
       </c>
       <c r="B88">
-        <v>2300</v>
+        <v>787</v>
       </c>
       <c r="C88">
-        <v>164.45</v>
+        <v>567.74</v>
       </c>
       <c r="D88">
-        <v>667</v>
+        <v>8082.49</v>
       </c>
       <c r="E88">
-        <v>378235</v>
+        <v>446811.38</v>
       </c>
       <c r="F88" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G88" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H88">
         <v>1</v>
       </c>
       <c r="I88">
-        <v>378235</v>
+        <v>446811.38</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89" t="s">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="B89">
-        <v>218100</v>
+        <v>50</v>
       </c>
       <c r="C89">
-        <v>4.34</v>
+        <v>45.97</v>
       </c>
       <c r="D89">
-        <v>-1699.04</v>
+        <v>72</v>
       </c>
       <c r="E89">
-        <v>946554</v>
+        <v>2298.5</v>
       </c>
       <c r="F89" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="G89" t="s">
-        <v>88</v>
+        <v>106</v>
       </c>
       <c r="H89">
-        <v>0.779</v>
+        <v>1</v>
       </c>
       <c r="I89">
-        <v>737365.5699999999</v>
+        <v>2298.5</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90" t="s">
-        <v>81</v>
+        <v>67</v>
       </c>
       <c r="B90">
-        <v>458570</v>
+        <v>100</v>
       </c>
       <c r="C90">
-        <v>100.46</v>
+        <v>62.36</v>
       </c>
       <c r="D90">
-        <v>103072.05</v>
+        <v>-34</v>
       </c>
       <c r="E90">
-        <v>46067942.2</v>
+        <v>6236</v>
       </c>
       <c r="F90" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="G90" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H90">
         <v>1</v>
       </c>
       <c r="I90">
-        <v>46067942.2</v>
+        <v>6236</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91" t="s">
-        <v>82</v>
+        <v>68</v>
       </c>
       <c r="B91">
-        <v>270</v>
+        <v>5200</v>
       </c>
       <c r="C91">
-        <v>42.08</v>
+        <v>29.33</v>
       </c>
       <c r="D91">
-        <v>40.97</v>
+        <v>2869.31</v>
       </c>
       <c r="E91">
-        <v>11361.6</v>
+        <v>152516</v>
       </c>
       <c r="F91" t="s">
-        <v>87</v>
+        <v>103</v>
       </c>
       <c r="G91" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
       <c r="H91">
-        <v>1</v>
+        <v>0.779</v>
       </c>
       <c r="I91">
-        <v>11361.6</v>
+        <v>118809.96</v>
       </c>
     </row>
     <row r="92" spans="1:9">
       <c r="A92" t="s">
+        <v>69</v>
+      </c>
+      <c r="B92">
+        <v>34</v>
+      </c>
+      <c r="C92">
+        <v>359.49</v>
+      </c>
+      <c r="D92">
+        <v>-107.78</v>
+      </c>
+      <c r="E92">
+        <v>12222.66</v>
+      </c>
+      <c r="F92" t="s">
+        <v>104</v>
+      </c>
+      <c r="G92" t="s">
+        <v>106</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>12222.66</v>
+      </c>
+    </row>
+    <row r="93" spans="1:9">
+      <c r="A93" t="s">
+        <v>70</v>
+      </c>
+      <c r="B93">
+        <v>10</v>
+      </c>
+      <c r="C93">
+        <v>103.92</v>
+      </c>
+      <c r="D93">
+        <v>-13.4</v>
+      </c>
+      <c r="E93">
+        <v>1039.2</v>
+      </c>
+      <c r="F93" t="s">
+        <v>104</v>
+      </c>
+      <c r="G93" t="s">
+        <v>106</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>1039.2</v>
+      </c>
+    </row>
+    <row r="94" spans="1:9">
+      <c r="A94" t="s">
+        <v>71</v>
+      </c>
+      <c r="B94">
+        <v>45900</v>
+      </c>
+      <c r="C94">
+        <v>714.65</v>
+      </c>
+      <c r="D94">
+        <v>-121635</v>
+      </c>
+      <c r="E94">
+        <v>32802435</v>
+      </c>
+      <c r="F94" t="s">
+        <v>104</v>
+      </c>
+      <c r="G94" t="s">
+        <v>106</v>
+      </c>
+      <c r="H94">
+        <v>1</v>
+      </c>
+      <c r="I94">
+        <v>32802435</v>
+      </c>
+    </row>
+    <row r="95" spans="1:9">
+      <c r="A95" t="s">
+        <v>72</v>
+      </c>
+      <c r="B95">
+        <v>54654</v>
+      </c>
+      <c r="C95">
+        <v>294.26</v>
+      </c>
+      <c r="D95">
+        <v>-59572.86</v>
+      </c>
+      <c r="E95">
+        <v>16082486.04</v>
+      </c>
+      <c r="F95" t="s">
+        <v>104</v>
+      </c>
+      <c r="G95" t="s">
+        <v>106</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>16082486.04</v>
+      </c>
+    </row>
+    <row r="96" spans="1:9">
+      <c r="A96" t="s">
+        <v>73</v>
+      </c>
+      <c r="B96">
+        <v>4320</v>
+      </c>
+      <c r="C96">
+        <v>223.25</v>
+      </c>
+      <c r="D96">
+        <v>4060.8</v>
+      </c>
+      <c r="E96">
+        <v>964440</v>
+      </c>
+      <c r="F96" t="s">
+        <v>104</v>
+      </c>
+      <c r="G96" t="s">
+        <v>106</v>
+      </c>
+      <c r="H96">
+        <v>1</v>
+      </c>
+      <c r="I96">
+        <v>964440</v>
+      </c>
+    </row>
+    <row r="97" spans="1:9">
+      <c r="A97" t="s">
+        <v>74</v>
+      </c>
+      <c r="B97">
+        <v>76900</v>
+      </c>
+      <c r="C97">
+        <v>24.32</v>
+      </c>
+      <c r="D97">
+        <v>18571.06</v>
+      </c>
+      <c r="E97">
+        <v>1870208</v>
+      </c>
+      <c r="F97" t="s">
+        <v>103</v>
+      </c>
+      <c r="G97" t="s">
+        <v>106</v>
+      </c>
+      <c r="H97">
+        <v>0.779</v>
+      </c>
+      <c r="I97">
+        <v>1456892.03</v>
+      </c>
+    </row>
+    <row r="98" spans="1:9">
+      <c r="A98" t="s">
+        <v>75</v>
+      </c>
+      <c r="B98">
+        <v>718033</v>
+      </c>
+      <c r="C98">
+        <v>33.7</v>
+      </c>
+      <c r="D98">
+        <v>43081.98</v>
+      </c>
+      <c r="E98">
+        <v>24197712.1</v>
+      </c>
+      <c r="F98" t="s">
+        <v>104</v>
+      </c>
+      <c r="G98" t="s">
+        <v>106</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98">
+        <v>24197712.1</v>
+      </c>
+    </row>
+    <row r="99" spans="1:9">
+      <c r="A99" t="s">
+        <v>76</v>
+      </c>
+      <c r="B99">
+        <v>8200</v>
+      </c>
+      <c r="C99">
+        <v>108.5923</v>
+      </c>
+      <c r="D99">
+        <v>-145.14</v>
+      </c>
+      <c r="E99">
+        <v>890456.86</v>
+      </c>
+      <c r="F99" t="s">
+        <v>104</v>
+      </c>
+      <c r="G99" t="s">
+        <v>106</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>890456.86</v>
+      </c>
+    </row>
+    <row r="100" spans="1:9">
+      <c r="A100" t="s">
+        <v>77</v>
+      </c>
+      <c r="B100">
+        <v>26</v>
+      </c>
+      <c r="C100">
+        <v>33.15</v>
+      </c>
+      <c r="D100">
+        <v>12.07</v>
+      </c>
+      <c r="E100">
+        <v>861.9</v>
+      </c>
+      <c r="F100" t="s">
+        <v>105</v>
+      </c>
+      <c r="G100" t="s">
+        <v>106</v>
+      </c>
+      <c r="H100">
+        <v>1.3454</v>
+      </c>
+      <c r="I100">
+        <v>1159.6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:9">
+      <c r="A101" t="s">
+        <v>78</v>
+      </c>
+      <c r="B101">
+        <v>100</v>
+      </c>
+      <c r="C101">
+        <v>67.78</v>
+      </c>
+      <c r="D101">
+        <v>41</v>
+      </c>
+      <c r="E101">
+        <v>6778</v>
+      </c>
+      <c r="F101" t="s">
+        <v>104</v>
+      </c>
+      <c r="G101" t="s">
+        <v>106</v>
+      </c>
+      <c r="H101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>6778</v>
+      </c>
+    </row>
+    <row r="102" spans="1:9">
+      <c r="A102" t="s">
+        <v>79</v>
+      </c>
+      <c r="B102">
+        <v>20100</v>
+      </c>
+      <c r="C102">
+        <v>2.27</v>
+      </c>
+      <c r="D102">
+        <v>402</v>
+      </c>
+      <c r="E102">
+        <v>45627</v>
+      </c>
+      <c r="F102" t="s">
+        <v>104</v>
+      </c>
+      <c r="G102" t="s">
+        <v>106</v>
+      </c>
+      <c r="H102">
+        <v>1</v>
+      </c>
+      <c r="I102">
+        <v>45627</v>
+      </c>
+    </row>
+    <row r="103" spans="1:9">
+      <c r="A103" t="s">
+        <v>80</v>
+      </c>
+      <c r="B103">
+        <v>18000</v>
+      </c>
+      <c r="C103">
+        <v>571.48</v>
+      </c>
+      <c r="D103">
+        <v>32040</v>
+      </c>
+      <c r="E103">
+        <v>10286640</v>
+      </c>
+      <c r="F103" t="s">
+        <v>104</v>
+      </c>
+      <c r="G103" t="s">
+        <v>106</v>
+      </c>
+      <c r="H103">
+        <v>1</v>
+      </c>
+      <c r="I103">
+        <v>10286640</v>
+      </c>
+    </row>
+    <row r="104" spans="1:9">
+      <c r="A104" t="s">
+        <v>81</v>
+      </c>
+      <c r="B104">
+        <v>15</v>
+      </c>
+      <c r="C104">
+        <v>149.1</v>
+      </c>
+      <c r="D104">
+        <v>-17.55</v>
+      </c>
+      <c r="E104">
+        <v>2236.5</v>
+      </c>
+      <c r="F104" t="s">
+        <v>104</v>
+      </c>
+      <c r="G104" t="s">
+        <v>106</v>
+      </c>
+      <c r="H104">
+        <v>1</v>
+      </c>
+      <c r="I104">
+        <v>2236.5</v>
+      </c>
+    </row>
+    <row r="105" spans="1:9">
+      <c r="A105" t="s">
+        <v>82</v>
+      </c>
+      <c r="B105">
+        <v>2</v>
+      </c>
+      <c r="C105">
+        <v>291.2</v>
+      </c>
+      <c r="D105">
+        <v>-3.3</v>
+      </c>
+      <c r="E105">
+        <v>582.4</v>
+      </c>
+      <c r="F105" t="s">
+        <v>104</v>
+      </c>
+      <c r="G105" t="s">
+        <v>106</v>
+      </c>
+      <c r="H105">
+        <v>1</v>
+      </c>
+      <c r="I105">
+        <v>582.4</v>
+      </c>
+    </row>
+    <row r="106" spans="1:9">
+      <c r="A106" t="s">
         <v>83</v>
       </c>
-      <c r="B92">
+      <c r="B106">
+        <v>87087</v>
+      </c>
+      <c r="C106">
+        <v>72.03</v>
+      </c>
+      <c r="D106">
+        <v>-70540.47</v>
+      </c>
+      <c r="E106">
+        <v>6272876.61</v>
+      </c>
+      <c r="F106" t="s">
+        <v>104</v>
+      </c>
+      <c r="G106" t="s">
+        <v>106</v>
+      </c>
+      <c r="H106">
+        <v>1</v>
+      </c>
+      <c r="I106">
+        <v>6272876.61</v>
+      </c>
+    </row>
+    <row r="107" spans="1:9">
+      <c r="A107" t="s">
+        <v>84</v>
+      </c>
+      <c r="B107">
+        <v>150200</v>
+      </c>
+      <c r="C107">
+        <v>43.58</v>
+      </c>
+      <c r="D107">
+        <v>60844.58</v>
+      </c>
+      <c r="E107">
+        <v>6545716</v>
+      </c>
+      <c r="F107" t="s">
+        <v>103</v>
+      </c>
+      <c r="G107" t="s">
+        <v>106</v>
+      </c>
+      <c r="H107">
+        <v>0.779</v>
+      </c>
+      <c r="I107">
+        <v>5099112.76</v>
+      </c>
+    </row>
+    <row r="108" spans="1:9">
+      <c r="A108" t="s">
+        <v>85</v>
+      </c>
+      <c r="B108">
+        <v>534400</v>
+      </c>
+      <c r="C108">
+        <v>5.59</v>
+      </c>
+      <c r="D108">
+        <v>-8326.17</v>
+      </c>
+      <c r="E108">
+        <v>2987296</v>
+      </c>
+      <c r="F108" t="s">
+        <v>103</v>
+      </c>
+      <c r="G108" t="s">
+        <v>106</v>
+      </c>
+      <c r="H108">
+        <v>0.779</v>
+      </c>
+      <c r="I108">
+        <v>2327103.58</v>
+      </c>
+    </row>
+    <row r="109" spans="1:9">
+      <c r="A109" t="s">
+        <v>86</v>
+      </c>
+      <c r="B109">
+        <v>1</v>
+      </c>
+      <c r="C109">
         <v>100</v>
       </c>
-      <c r="C92">
+      <c r="D109">
+        <v>0.31</v>
+      </c>
+      <c r="E109">
+        <v>100</v>
+      </c>
+      <c r="F109" t="s">
+        <v>104</v>
+      </c>
+      <c r="G109" t="s">
+        <v>106</v>
+      </c>
+      <c r="H109">
+        <v>1</v>
+      </c>
+      <c r="I109">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="110" spans="1:9">
+      <c r="A110" t="s">
+        <v>87</v>
+      </c>
+      <c r="B110">
+        <v>10</v>
+      </c>
+      <c r="C110">
+        <v>164.12</v>
+      </c>
+      <c r="D110">
+        <v>25.5</v>
+      </c>
+      <c r="E110">
+        <v>1641.2</v>
+      </c>
+      <c r="F110" t="s">
+        <v>104</v>
+      </c>
+      <c r="G110" t="s">
+        <v>106</v>
+      </c>
+      <c r="H110">
+        <v>1</v>
+      </c>
+      <c r="I110">
+        <v>1641.2</v>
+      </c>
+    </row>
+    <row r="111" spans="1:9">
+      <c r="A111" t="s">
+        <v>88</v>
+      </c>
+      <c r="B111">
+        <v>1000</v>
+      </c>
+      <c r="C111">
+        <v>24.01</v>
+      </c>
+      <c r="D111">
+        <v>-159.9</v>
+      </c>
+      <c r="E111">
+        <v>24010</v>
+      </c>
+      <c r="F111" t="s">
+        <v>104</v>
+      </c>
+      <c r="G111" t="s">
+        <v>106</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>24010</v>
+      </c>
+    </row>
+    <row r="112" spans="1:9">
+      <c r="A112" t="s">
+        <v>89</v>
+      </c>
+      <c r="B112">
+        <v>21</v>
+      </c>
+      <c r="C112">
+        <v>275.17</v>
+      </c>
+      <c r="D112">
+        <v>-58.17</v>
+      </c>
+      <c r="E112">
+        <v>5778.57</v>
+      </c>
+      <c r="F112" t="s">
+        <v>104</v>
+      </c>
+      <c r="G112" t="s">
+        <v>106</v>
+      </c>
+      <c r="H112">
+        <v>1</v>
+      </c>
+      <c r="I112">
+        <v>5778.57</v>
+      </c>
+    </row>
+    <row r="113" spans="1:9">
+      <c r="A113" t="s">
+        <v>90</v>
+      </c>
+      <c r="B113">
+        <v>10</v>
+      </c>
+      <c r="C113">
+        <v>141.38</v>
+      </c>
+      <c r="D113">
+        <v>8</v>
+      </c>
+      <c r="E113">
+        <v>1413.8</v>
+      </c>
+      <c r="F113" t="s">
+        <v>104</v>
+      </c>
+      <c r="G113" t="s">
+        <v>106</v>
+      </c>
+      <c r="H113">
+        <v>1</v>
+      </c>
+      <c r="I113">
+        <v>1413.8</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9">
+      <c r="A114" t="s">
+        <v>91</v>
+      </c>
+      <c r="B114">
+        <v>105000</v>
+      </c>
+      <c r="C114">
+        <v>164.77</v>
+      </c>
+      <c r="D114">
+        <v>-37800</v>
+      </c>
+      <c r="E114">
+        <v>17300850</v>
+      </c>
+      <c r="F114" t="s">
+        <v>104</v>
+      </c>
+      <c r="G114" t="s">
+        <v>106</v>
+      </c>
+      <c r="H114">
+        <v>1</v>
+      </c>
+      <c r="I114">
+        <v>17300850</v>
+      </c>
+    </row>
+    <row r="115" spans="1:9">
+      <c r="A115" t="s">
+        <v>92</v>
+      </c>
+      <c r="B115">
+        <v>6003</v>
+      </c>
+      <c r="C115">
+        <v>46.99</v>
+      </c>
+      <c r="D115">
+        <v>3121.56</v>
+      </c>
+      <c r="E115">
+        <v>282080.97</v>
+      </c>
+      <c r="F115" t="s">
+        <v>104</v>
+      </c>
+      <c r="G115" t="s">
+        <v>106</v>
+      </c>
+      <c r="H115">
+        <v>1</v>
+      </c>
+      <c r="I115">
+        <v>282080.97</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9">
+      <c r="A116" t="s">
+        <v>93</v>
+      </c>
+      <c r="B116">
+        <v>28600</v>
+      </c>
+      <c r="C116">
+        <v>85.11</v>
+      </c>
+      <c r="D116">
+        <v>-6292</v>
+      </c>
+      <c r="E116">
+        <v>2434146</v>
+      </c>
+      <c r="F116" t="s">
+        <v>104</v>
+      </c>
+      <c r="G116" t="s">
+        <v>106</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="I116">
+        <v>2434146</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9">
+      <c r="A117" t="s">
+        <v>94</v>
+      </c>
+      <c r="B117">
+        <v>2300</v>
+      </c>
+      <c r="C117">
+        <v>164.45</v>
+      </c>
+      <c r="D117">
+        <v>667</v>
+      </c>
+      <c r="E117">
+        <v>378235</v>
+      </c>
+      <c r="F117" t="s">
+        <v>104</v>
+      </c>
+      <c r="G117" t="s">
+        <v>106</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117">
+        <v>378235</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" t="s">
+        <v>95</v>
+      </c>
+      <c r="B118">
+        <v>218100</v>
+      </c>
+      <c r="C118">
+        <v>4.34</v>
+      </c>
+      <c r="D118">
+        <v>-1699.04</v>
+      </c>
+      <c r="E118">
+        <v>946554</v>
+      </c>
+      <c r="F118" t="s">
+        <v>103</v>
+      </c>
+      <c r="G118" t="s">
+        <v>106</v>
+      </c>
+      <c r="H118">
+        <v>0.779</v>
+      </c>
+      <c r="I118">
+        <v>737365.5699999999</v>
+      </c>
+    </row>
+    <row r="119" spans="1:9">
+      <c r="A119" t="s">
+        <v>96</v>
+      </c>
+      <c r="B119">
+        <v>458570</v>
+      </c>
+      <c r="C119">
+        <v>100.46</v>
+      </c>
+      <c r="D119">
+        <v>103072.05</v>
+      </c>
+      <c r="E119">
+        <v>46067942.2</v>
+      </c>
+      <c r="F119" t="s">
+        <v>104</v>
+      </c>
+      <c r="G119" t="s">
+        <v>107</v>
+      </c>
+      <c r="H119">
+        <v>1</v>
+      </c>
+      <c r="I119">
+        <v>46067942.2</v>
+      </c>
+    </row>
+    <row r="120" spans="1:9">
+      <c r="A120" t="s">
+        <v>97</v>
+      </c>
+      <c r="B120">
+        <v>270</v>
+      </c>
+      <c r="C120">
+        <v>42.08</v>
+      </c>
+      <c r="D120">
+        <v>40.97</v>
+      </c>
+      <c r="E120">
+        <v>11361.6</v>
+      </c>
+      <c r="F120" t="s">
+        <v>104</v>
+      </c>
+      <c r="G120" t="s">
+        <v>107</v>
+      </c>
+      <c r="H120">
+        <v>1</v>
+      </c>
+      <c r="I120">
+        <v>11361.6</v>
+      </c>
+    </row>
+    <row r="121" spans="1:9">
+      <c r="A121" t="s">
+        <v>98</v>
+      </c>
+      <c r="B121">
+        <v>100</v>
+      </c>
+      <c r="C121">
         <v>75.90000000000001</v>
       </c>
-      <c r="D92">
+      <c r="D121">
         <v>-13</v>
       </c>
-      <c r="E92">
+      <c r="E121">
         <v>7590</v>
       </c>
-      <c r="F92" t="s">
-        <v>87</v>
-      </c>
-      <c r="G92" t="s">
-        <v>90</v>
-      </c>
-      <c r="H92">
-        <v>1</v>
-      </c>
-      <c r="I92">
+      <c r="F121" t="s">
+        <v>104</v>
+      </c>
+      <c r="G121" t="s">
+        <v>108</v>
+      </c>
+      <c r="H121">
+        <v>1</v>
+      </c>
+      <c r="I121">
         <v>7590</v>
       </c>
     </row>
